--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07</t>
+          <t>2026-09-13 08:31</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-13 08:31</t>
+          <t>2026-09-14 09:14</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-14 09:14</t>
+          <t>2026-09-15 08:56</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-15 08:56</t>
+          <t>2026-09-16 08:49</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-16 08:49</t>
+          <t>2026-09-17 08:53</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-17 08:53</t>
+          <t>2026-09-18 08:28</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:28</t>
+          <t>2026-09-19 08:16</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-19 08:16</t>
+          <t>2026-09-20 08:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-20 08:48</t>
+          <t>2026-09-21 09:16</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16</t>
+          <t>2026-09-22 08:47</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47</t>
+          <t>2026-09-23 08:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -413,13 +413,5110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ціна</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ціна за літр</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Обсяг</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Діюча речовина</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Бренд</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Дата_парсінгу</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Бастіон</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1 584.00 грн</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>316.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ципроконазол 6,3г</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-bast-on</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Диквалан</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3 114.00 грн</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>155.7 грн/л</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>дикват 150г</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-dikvalan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Дот</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3 148.00 грн</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>629.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ципроконазол 80г</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-dot</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Мачо</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>690.00 грн</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>138.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>етоксилат ізодецилового спирту 900г</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-macho</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Напалм, ВР</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3 424.00 грн</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>171.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ізопропіламінна сіль гліфосату 480г</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-napalm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Октант, ВГ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>287.00 грн</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>574.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>тіаметоксам 250г</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-oktant-vg___</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Бомбардир</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>187.00 грн</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>748.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.25 кг</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>імідаклоприд 700г</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-bombardir__</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Напалм Форте, ВК</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4 429.00 грн</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>221.45 грн/л</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>калійна сіль гліфосату 550г</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-napalm-forte</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Спліт Дуо</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3 128.00 грн</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>625.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>дифеноконазол 125г</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-spl-t-dyo-am-star-gold</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Супер-Мачо</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2 515.00 грн</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>503.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>модифікований поліефір трісілоксан 85% + аллілоксіполіетиленгліколь  л</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-syper-macho</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Фуксія, ТН</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2 515.00 грн</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>503.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>флудіоксоніл 25г</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-fyks-ya-tn</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Атік, ВП</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>180.00 грн</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>720.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>фольгований пакет 250 г</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ацетаміприд 200г</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-at-k-vp_</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Напалм Супер</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5 171.00 грн</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>258.55 грн/л</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>калійна сіль гліфосату 663г</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-napalm-syper-rayndap-ekstra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Піногасник Пайот Ультра</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>671.00 грн</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>671.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1 л</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>модифікований поліефір трісілоксан 50 %</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-p-nogasnik-paiot-yltra</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Сигма</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3 082.00 грн</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>616.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>азоксистробін 200г</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sigma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Атік Макс</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3 155.00 грн</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>631.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ацетаміприд 300г</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-at-k-maks</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Блейд</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3 241.00 грн</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>324.1 грн/л</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>клетодим 120г</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-bleid</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Радикал Нео</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6 627.00 грн</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1325.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>азоксистробін 250г</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-radikal-neo</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Октант Турбо</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3 072.00 грн</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>614.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>тіаметоксам 141г</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-oktant-tyrbo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Палдіс</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2 219.00 грн</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2219.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>пакет 1 кг</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>темботріон 200г</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-pald-s</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Міральд, КС</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1 854.00 грн</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>370.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>фенпіроксимат 50г</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-mirald-ks__</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Муссон</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2 793.00 грн</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>279.3 грн/л</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>нікосульфурон 40г</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-mysson</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Просенс</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1 399.00 грн</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1399.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>пакет 1 кг</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>емамектин бензоат 100г</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-prosens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Сумаро</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4 836.00 грн</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>967.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>мезотріон 480г</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-symaro-ks</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Твікс</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7 369.00 грн</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>368.45 грн/л</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>хлорпірифос 500г</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-tv-ks_</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Харума Макс</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3 911.00 грн</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>391.1 грн/л</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>хізалофоп-П-етил 150г</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-haryma-maks</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Абсолют</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1 482.00 грн</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>296.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>карбендазим 500г</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-absolut</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Абсолют, КС (Дерозал)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1 482.00 грн</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>296.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>карбендазим 500г</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-absolut-ks</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Айлар</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16 325.00 грн</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>816.25 грн/л</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>аклоніфен 600г</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-ailar-ks</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>АКСАКАЛ</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1 862.00 грн</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3724.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>флорасулам 250г</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-aksakal____</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Альтрон, КС</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2 141.00 грн</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>428.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>альфа-циперметрин 200г</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-altron-ks</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Альфа Супер</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1 469.00 грн</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>293.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>альфа-циперметрин 100г</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-alfa-syper</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Арес, ТН</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4 749.00 грн</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>949.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>металаксил-М 350г</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-ares-tn</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Атік, ВП</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>252.00 грн</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>504.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ацетаміприд 200г</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-at-k-vp______</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Бантен</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>8 186.00 грн</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>409.3 грн/л</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>бентазон 480г</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-banten-rk</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Бетагард</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>9 831.00 грн</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>491.55 грн/л</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>фенмедифам 91г</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-betagard</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Бомбардир Аква</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1 675.00 грн</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>335.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>імідаклоприд 200г</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-bombardir-akva_</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Бомбардир Дуо</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2 793.00 грн</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>558.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>імідаклоприд 300г</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-bombardir-dyo</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Брокс, РК</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2 138.00 грн</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>427.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>імазамокс 40г</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-broks-rk_</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Велас</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16 198.00 грн</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>809.9 грн/л</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>продукт ферментації гриба Steptomyces kasugaensis 60г</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-velas</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Вертекс</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1 761.00 грн</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>352.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>поліетиленгліколь-400 230г</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-verteks_</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Даблтрай</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>6 917.00 грн</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>345.85 грн/л</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>метолахлор 960г</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-dabl-trai</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Дикамба Форте</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5 473.00 грн</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>273.65 грн/л</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>дикамба у формі диметиламінної солі 120г</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-dikamba-forte</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Диквалан Макс</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5 142.00 грн</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>257.1 грн/л</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>дикват дибромід 374г</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-dikvalan-maks</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ефімер</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1 453.00 грн</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>290.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-ef-mer_</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Імпреза</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10 428.00 грн</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>521.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>імазамокс 33г</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-mpreza</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Кайрос</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>31 651.00 грн</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6330.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>флубендіамід 480г</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-kairos</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Камзол Турбо</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5 214.00 грн</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1042.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ципроконазол 80г</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-kamzol-tyrbo</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Камзол, РК</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4 842.00 грн</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>968.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>метконазол 60г</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-kamzol-rk</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Кентавр</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3 352.00 грн</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6704.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>римсульфурон 500г</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-kentavr____</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Клаттер, КЕ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2 328.00 грн</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>465.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>кломазон 480г</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-klatter-ke</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Кушон, КС</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4 831.00 грн</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>966.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>метамітрон 700г</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-kyshon-ks__</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Латіна, ТН</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6 704.00 грн</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1340.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>клотіанідин 600г</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-latina-tn</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Літерон</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7 187.00 грн</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>359.35 грн/л</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>S-метолахлор 960г</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-l-teron</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Матар, КС</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>4 372.00 грн</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>874.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>метрибузин 600г</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-matar-ks</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Метакса</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2 328.00 грн</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>465.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>тіаметоксам 350г</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-metaksa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Меценат</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2 328.00 грн</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>465.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>пропіконазол 250г</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-mecenat_</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Напалм</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3 424.00 грн</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>171.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ізопропіламінна сіль гліфосату 480г</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-napalm_</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Напалм Форте</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4 424.00 грн</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>221.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>калійна сіль гліфосату 550г</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-napalm-forte_</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Нованте</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>6 517.00 грн</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>325.85 грн/л</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>S-метолахлор 312,5г</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-novante</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Оіл-Дріфт</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5 560.00 грн</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>278.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ріпаково-метиловий ефір 810г</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-o-l-dr-ft</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Парацельс</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2 328.00 грн</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>465.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>флутріафол 250г</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-paracels</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Пегас, КЕ</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2 328.00 грн</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>465.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>прохлораз 450г</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-pegas-ke_</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Перун</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5 203.00 грн</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>260.15 грн/л</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>прометрин 500г</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-peryn</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Піногасник Пайот</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>615.00 грн</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>615.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1 л</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>модифікований поліефір трісілоксан 10-20 % л</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-paiot</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Піраміда</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2 716.00 грн</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>543.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>клопіралід 300г</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-p-ram-da-lontrel</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Престо</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3 446.00 грн</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>689.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>клотіанідин 200г</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-presto_</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Примус, СЕ</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1 293.00 грн</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>258.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2-етилгексиловий ефір 2,4-Д 452г</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-primys_</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Просенс</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1 416.00 грн</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2832.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>емамектин бензоат 100г</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-prostaf</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Равак</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>358.00 грн</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>358.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1 кг</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-ravak</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Рим</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1 676.00 грн</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3352.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>римсульфурон 250г</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-rim___</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Сальто, КС</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1 843.00 грн</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>368.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>тіофанат-метил 500г</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-salto-ks_</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Сахара</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5 579.00 грн</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>278.95 грн/л</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ацетохлор 900г</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sahara</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Сахара Супер</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7 439.00 грн</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>371.95 грн/л</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ацетохлор 800г</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sahara-syper</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Синерид, МД</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5 208.00 грн</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1041.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>тіаклоприд 240г</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sinerid-md_</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Сілтек</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2 413.00 грн</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>482.6 грн/л</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>суміш клеючих та поверхнево-активних речовин 60% р-н</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-s-ltek</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Спліт</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3 631.00 грн</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>726.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>дифеконазол 250г</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-spl-t</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Старк, КС</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2 904.00 грн</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>580.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>азоксистробін 250г</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-stark-ks</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Тава, РК</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1 490.00 грн</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>298.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>етефон 480г</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-tava-rk_</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Талер Макс</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2 515.00 грн</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>503.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>тебуконазол 500г</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-taler-maks</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Талер, КЕ</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2 102.00 грн</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>420.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>тебуконазол 250г</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-taler-ke__</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Топал</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5 177.00 грн</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1035.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>трінексапак-етил 250г</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-topal</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ультралін</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1 282.00 грн</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1282.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1 кг</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>цимоксаніл 300г</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-yltral-n</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Форит</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2 969.00 грн</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>593.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>каністра 5 л</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>флуроксипір 333г</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-forit</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Харума</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3 537.00 грн</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>353.7 грн/л</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>хізалофоп-П-етил 125г</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-haryma</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Хлорис, ЕН</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1 482.00 грн</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>296.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>тебуконазол 15г</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-hloris-en__</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Циркуль, КЕ</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1 295.00 грн</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>259.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>лямбда-цигалотрин 50г</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-cirkyl-ke</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Шериф Максі</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1 676.00 грн</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3352.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>трибенурон-метил 563г</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sherif-maks</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Шериф, ВГ</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>651.00 грн</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1302.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0.5 л</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>трибенурон-метил 750г</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sherif</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Шериф, ВГ</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>651.00 грн</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1302.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>трибенурон-метил 750г</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sherif__</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>АЙДАХО</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5 537.00 грн</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>276.85 грн/л</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>тербутилазин 500г</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-aidaho</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>АЙДАХО</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1 562.00 грн</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>312.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>тербутилазин 500г</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-aidaho_</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>АЙДАХО</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3 032.00 грн</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>303.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>тербутилазин 500г</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-aidaho__</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Атік, ВП</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>442.00 грн</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>4420.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>10 пакетів по 100 г - 1 кг</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ацетаміприд 200г</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-at-k-vp_____</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Блейд</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1 674.00 грн</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>334.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>клетодим 120г</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-bleid_</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Бомбардир Аква</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>4 682.00 грн</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>468.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>імідаклоприд 200г</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-bombardir-akva</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Брокс, РК</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4 685.00 грн</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>468.5 грн/л</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>імазамокс 40г</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-broks-rk__</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Ефімер</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>6 157.00 грн</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>307.85 грн/л</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-ef-mer</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Кушон, КС</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>9 529.00 грн</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>952.9 грн/л</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>метамітрон 700г</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-kyshon-ks_</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Латіна, ТН</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>33 904.00 грн</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1695.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>клотіанідин 600г</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-lat-na-tn</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Метакса</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>12 491.00 грн</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>624.55 грн/л</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>тіаметоксам 350г</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-metaksa_</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Меценат</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5 710.00 грн</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>571.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>пропіконазол 250г</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-mecenat</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Міральд, КС</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>4 015.00 грн</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>401.5 грн/л</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>фенпіроксимат 50г</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-mirald-ks___</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Напалм</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>937.00 грн</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>187.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ізопропіламінна сіль гліфосату 480г</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-napalm___</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Напалм, ВР</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>937.00 грн</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>187.4 грн/л</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ізопропіламінна сіль гліфосату 480г</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-napalm__</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Панголін, ВГ</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2 762.00 грн</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>4603.33 грн/кг</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>фольгований пакет 0.6 кг</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>трифлусульфурон-метил 500г</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-pangol-n-vg__</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Перун</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1 451.00 грн</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>290.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>прометрин 500г</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-peryn_</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Піногасник Пайот</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>137.00 грн</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>685.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.2 л</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>модифікований поліефір трісілоксан 10-20 % л</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-p-nogasnik-paiot</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Престо</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>16 060.00 грн</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>803.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>клотіанідин 200г</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-presto</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Престо</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>821.00 грн</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>821.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1 л</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>клотіанідин 200г</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-presto__</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Сора-Нет</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5 899.00 грн</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>294.95 грн/л</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>пропізохлор 720г</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sora-net</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Сора-Нет</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>3 792.00 грн</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>379.2 грн/л</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>пропізохлор 720г</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-sora-net_</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Старлент</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>6 669.00 грн</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>333.45 грн/л</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>пропізохлор 360г</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-starlent</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Талер, КЕ</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4 417.00 грн</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>441.7 грн/л</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>тебуконазол 250г</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-taler-ke_</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Твікс</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>4 020.00 грн</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>402.0 грн/л</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>хлорпірифос 500г</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-tv-ks</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Тирана</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>імідаклоприд 280г</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-tirana</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Тринол</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1 кг</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>фенгексамід 500г</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-trinol</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Фуксія, ТН</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>11 154.00 грн</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>557.7 грн/л</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>20 л</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>флудіоксоніл 25г</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-fyks-ya-tn_</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Фумігант 56 %</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>650.00 грн</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>650.0 грн/кг</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>флакон 1 кг</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>фосфід алюмінію 560г</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-fumigant-56</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Харума</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2 209.00 грн</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>441.8 грн/л</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>5 л</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>хізалофоп-П-етил 125г</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-haryma_</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Хлорис, ЕН</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>3 079.00 грн</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>307.9 грн/л</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>10 л</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>тебуконазол 15г</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>DEFENDA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://lnzweb.com/product-hloris-en_</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:04</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-25 09:04</t>
+          <t>2026-09-26 08:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48</t>
+          <t>2026-09-27 09:30</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30</t>
+          <t>2026-09-28 10:07</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-28 10:07</t>
+          <t>2026-09-29 10:06</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-29 10:06</t>
+          <t>2026-09-30 09:58</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -3642,34 +3642,34 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Спліт</t>
+          <t>Сора-Нет</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3 631.00 грн</t>
+          <t>5 962.00 грн</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>726.2 грн/л</t>
+          <t>298.1 грн/л</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>дифеконазол 250г</t>
+          <t>пропізохлор 720г</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3679,29 +3679,29 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-spl-t</t>
+          <t>https://lnzweb.com/product-sora-net</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Старк, КС</t>
+          <t>Спліт</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2 904.00 грн</t>
+          <t>3 631.00 грн</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>580.8 грн/л</t>
+          <t>726.2 грн/л</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>азоксистробін 250г</t>
+          <t>дифеконазол 250г</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3721,29 +3721,29 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-stark-ks</t>
+          <t>https://lnzweb.com/product-spl-t</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Тава, РК</t>
+          <t>Старк, КС</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1 490.00 грн</t>
+          <t>2 904.00 грн</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>298.0 грн/л</t>
+          <t>580.8 грн/л</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>етефон 480г</t>
+          <t>азоксистробін 250г</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3763,29 +3763,29 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-tava-rk_</t>
+          <t>https://lnzweb.com/product-stark-ks</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Талер Макс</t>
+          <t>Тава, РК</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2 515.00 грн</t>
+          <t>1 490.00 грн</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>503.0 грн/л</t>
+          <t>298.0 грн/л</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>тебуконазол 500г</t>
+          <t>етефон 480г</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3805,29 +3805,29 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-taler-maks</t>
+          <t>https://lnzweb.com/product-tava-rk_</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Талер, КЕ</t>
+          <t>Талер Макс</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2 102.00 грн</t>
+          <t>2 515.00 грн</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>420.4 грн/л</t>
+          <t>503.0 грн/л</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>тебуконазол 250г</t>
+          <t>тебуконазол 500г</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3847,29 +3847,29 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-taler-ke__</t>
+          <t>https://lnzweb.com/product-taler-maks</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Топал</t>
+          <t>Талер, КЕ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5 177.00 грн</t>
+          <t>2 102.00 грн</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1035.4 грн/л</t>
+          <t>420.4 грн/л</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>трінексапак-етил 250г</t>
+          <t>тебуконазол 250г</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3889,39 +3889,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-topal</t>
+          <t>https://lnzweb.com/product-taler-ke__</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ультралін</t>
+          <t>Топал</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1 282.00 грн</t>
+          <t>5 177.00 грн</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1282.0 грн/кг</t>
+          <t>1035.4 грн/л</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>цимоксаніл 300г</t>
+          <t>трінексапак-етил 250г</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3931,39 +3931,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-yltral-n</t>
+          <t>https://lnzweb.com/product-topal</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Форит</t>
+          <t>Ультралін</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2 969.00 грн</t>
+          <t>1 282.00 грн</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>593.8 грн/л</t>
+          <t>1282.0 грн/кг</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>каністра 5 л</t>
+          <t>1 кг</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>флуроксипір 333г</t>
+          <t>цимоксаніл 300г</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3973,39 +3973,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-forit</t>
+          <t>https://lnzweb.com/product-yltral-n</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Харума</t>
+          <t>Форит</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3 537.00 грн</t>
+          <t>2 969.00 грн</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>353.7 грн/л</t>
+          <t>593.8 грн/л</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>каністра 5 л</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>хізалофоп-П-етил 125г</t>
+          <t>флуроксипір 333г</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4015,39 +4015,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-haryma</t>
+          <t>https://lnzweb.com/product-forit</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Хлорис, ЕН</t>
+          <t>Харума</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1 482.00 грн</t>
+          <t>3 537.00 грн</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>296.4 грн/л</t>
+          <t>353.7 грн/л</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>тебуконазол 15г</t>
+          <t>хізалофоп-П-етил 125г</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4057,29 +4057,29 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-hloris-en__</t>
+          <t>https://lnzweb.com/product-haryma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Циркуль, КЕ</t>
+          <t>Хлорис, ЕН</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1 295.00 грн</t>
+          <t>1 482.00 грн</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>259.0 грн/л</t>
+          <t>296.4 грн/л</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>лямбда-цигалотрин 50г</t>
+          <t>тебуконазол 15г</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4099,39 +4099,39 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-cirkyl-ke</t>
+          <t>https://lnzweb.com/product-hloris-en__</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Шериф Максі</t>
+          <t>Циркуль, КЕ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1 676.00 грн</t>
+          <t>1 295.00 грн</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3352.0 грн/кг</t>
+          <t>259.0 грн/л</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>трибенурон-метил 563г</t>
+          <t>лямбда-цигалотрин 50г</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4141,39 +4141,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sherif-maks</t>
+          <t>https://lnzweb.com/product-cirkyl-ke</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Шериф, ВГ</t>
+          <t>Шериф Максі</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>651.00 грн</t>
+          <t>1 676.00 грн</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1302.0 грн/л</t>
+          <t>3352.0 грн/кг</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>трибенурон-метил 750г</t>
+          <t>трибенурон-метил 563г</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sherif</t>
+          <t>https://lnzweb.com/product-sherif-maks</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -4205,12 +4205,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1302.0 грн/кг</t>
+          <t>1302.0 грн/л</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>0.5 л</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4225,39 +4225,39 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sherif__</t>
+          <t>https://lnzweb.com/product-sherif</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>АЙДАХО</t>
+          <t>Шериф, ВГ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5 537.00 грн</t>
+          <t>651.00 грн</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>276.85 грн/л</t>
+          <t>1302.0 грн/кг</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>тербутилазин 500г</t>
+          <t>трибенурон-метил 750г</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-aidaho</t>
+          <t>https://lnzweb.com/product-sherif__</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -4284,17 +4284,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1 562.00 грн</t>
+          <t>5 537.00 грн</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>312.4 грн/л</t>
+          <t>276.85 грн/л</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-aidaho_</t>
+          <t>https://lnzweb.com/product-aidaho</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -4326,17 +4326,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3 032.00 грн</t>
+          <t>1 562.00 грн</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>303.2 грн/л</t>
+          <t>312.4 грн/л</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4351,39 +4351,39 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-aidaho__</t>
+          <t>https://lnzweb.com/product-aidaho_</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Атік, ВП</t>
+          <t>АЙДАХО</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>442.00 грн</t>
+          <t>3 032.00 грн</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4420.0 грн/кг</t>
+          <t>303.2 грн/л</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10 пакетів по 100 г - 1 кг</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ацетаміприд 200г</t>
+          <t>тербутилазин 500г</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4393,39 +4393,39 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-at-k-vp_____</t>
+          <t>https://lnzweb.com/product-aidaho__</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Блейд</t>
+          <t>Атік, ВП</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1 674.00 грн</t>
+          <t>442.00 грн</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>334.8 грн/л</t>
+          <t>4420.0 грн/кг</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>10 пакетів по 100 г - 1 кг</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>клетодим 120г</t>
+          <t>ацетаміприд 200г</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4435,39 +4435,39 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-bleid_</t>
+          <t>https://lnzweb.com/product-at-k-vp_____</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Бомбардир Аква</t>
+          <t>Блейд</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4 682.00 грн</t>
+          <t>1 674.00 грн</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>468.2 грн/л</t>
+          <t>334.8 грн/л</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>імідаклоприд 200г</t>
+          <t>клетодим 120г</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4477,29 +4477,29 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-bombardir-akva</t>
+          <t>https://lnzweb.com/product-bleid_</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Брокс, РК</t>
+          <t>Бомбардир Аква</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4 685.00 грн</t>
+          <t>4 682.00 грн</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>468.5 грн/л</t>
+          <t>468.2 грн/л</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>імазамокс 40г</t>
+          <t>імідаклоприд 200г</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4519,39 +4519,39 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-broks-rk__</t>
+          <t>https://lnzweb.com/product-bombardir-akva</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ефімер</t>
+          <t>Брокс, РК</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6 157.00 грн</t>
+          <t>4 685.00 грн</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>307.85 грн/л</t>
+          <t>468.5 грн/л</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
+          <t>імазамокс 40г</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4561,39 +4561,39 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ef-mer</t>
+          <t>https://lnzweb.com/product-broks-rk__</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Кушон, КС</t>
+          <t>Ефімер</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>9 529.00 грн</t>
+          <t>6 157.00 грн</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>952.9 грн/л</t>
+          <t>307.85 грн/л</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>метамітрон 700г</t>
+          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4603,39 +4603,39 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kyshon-ks_</t>
+          <t>https://lnzweb.com/product-ef-mer</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Латіна, ТН</t>
+          <t>Кушон, КС</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>33 904.00 грн</t>
+          <t>9 529.00 грн</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1695.2 грн/л</t>
+          <t>952.9 грн/л</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>клотіанідин 600г</t>
+          <t>метамітрон 700г</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4645,29 +4645,29 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-lat-na-tn</t>
+          <t>https://lnzweb.com/product-kyshon-ks_</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Метакса</t>
+          <t>Латіна, ТН</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12 491.00 грн</t>
+          <t>33 904.00 грн</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>624.55 грн/л</t>
+          <t>1695.2 грн/л</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>тіаметоксам 350г</t>
+          <t>клотіанідин 600г</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4687,39 +4687,39 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-metaksa_</t>
+          <t>https://lnzweb.com/product-lat-na-tn</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Меценат</t>
+          <t>Метакса</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5 710.00 грн</t>
+          <t>12 491.00 грн</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>571.0 грн/л</t>
+          <t>624.55 грн/л</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>пропіконазол 250г</t>
+          <t>тіаметоксам 350г</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4729,29 +4729,29 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mecenat</t>
+          <t>https://lnzweb.com/product-metaksa_</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Міральд, КС</t>
+          <t>Меценат</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4 015.00 грн</t>
+          <t>5 710.00 грн</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>401.5 грн/л</t>
+          <t>571.0 грн/л</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>фенпіроксимат 50г</t>
+          <t>пропіконазол 250г</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4771,39 +4771,39 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mirald-ks___</t>
+          <t>https://lnzweb.com/product-mecenat</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Напалм</t>
+          <t>Міральд, КС</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>937.00 грн</t>
+          <t>4 015.00 грн</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>187.4 грн/л</t>
+          <t>401.5 грн/л</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ізопропіламінна сіль гліфосату 480г</t>
+          <t>фенпіроксимат 50г</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4813,19 +4813,19 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-napalm___</t>
+          <t>https://lnzweb.com/product-mirald-ks___</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Напалм, ВР</t>
+          <t>Напалм</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4855,39 +4855,39 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-napalm__</t>
+          <t>https://lnzweb.com/product-napalm___</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Панголін, ВГ</t>
+          <t>Напалм, ВР</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2 762.00 грн</t>
+          <t>937.00 грн</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4603.33 грн/кг</t>
+          <t>187.4 грн/л</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.6 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>трифлусульфурон-метил 500г</t>
+          <t>ізопропіламінна сіль гліфосату 480г</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4897,39 +4897,39 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-pangol-n-vg__</t>
+          <t>https://lnzweb.com/product-napalm__</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Перун</t>
+          <t>Панголін, ВГ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1 451.00 грн</t>
+          <t>2 762.00 грн</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>290.2 грн/л</t>
+          <t>4603.33 грн/кг</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.6 кг</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>прометрин 500г</t>
+          <t>трифлусульфурон-метил 500г</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4939,39 +4939,39 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-peryn_</t>
+          <t>https://lnzweb.com/product-pangol-n-vg__</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Піногасник Пайот</t>
+          <t>Перун</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>137.00 грн</t>
+          <t>1 451.00 грн</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>685.0 грн/л</t>
+          <t>290.2 грн/л</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0.2 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>модифікований поліефір трісілоксан 10-20 % л</t>
+          <t>прометрин 500г</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4981,39 +4981,39 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-p-nogasnik-paiot</t>
+          <t>https://lnzweb.com/product-peryn_</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Престо</t>
+          <t>Піногасник Пайот</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16 060.00 грн</t>
+          <t>137.00 грн</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>803.0 грн/л</t>
+          <t>685.0 грн/л</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>0.2 л</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>клотіанідин 200г</t>
+          <t>модифікований поліефір трісілоксан 10-20 % л</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-presto</t>
+          <t>https://lnzweb.com/product-p-nogasnik-paiot</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5040,17 +5040,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>821.00 грн</t>
+          <t>16 060.00 грн</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>821.0 грн/л</t>
+          <t>803.0 грн/л</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5065,39 +5065,39 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-presto__</t>
+          <t>https://lnzweb.com/product-presto</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Сора-Нет</t>
+          <t>Престо</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5 899.00 грн</t>
+          <t>821.00 грн</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>294.95 грн/л</t>
+          <t>821.0 грн/л</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>1 л</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>пропізохлор 720г</t>
+          <t>клотіанідин 200г</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sora-net</t>
+          <t>https://lnzweb.com/product-presto__</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58</t>
+          <t>2026-10-01 10:25</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25</t>
+          <t>2026-10-02 10:01</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-02 10:01</t>
+          <t>2026-10-03 09:24</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24</t>
+          <t>2026-10-04 10:03</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-04 10:03</t>
+          <t>2026-10-05 10:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -466,12 +466,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1 584.00 грн</t>
+          <t>1 640.00 грн</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>316.8 грн/л</t>
+          <t>328.0 грн/л</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3 114.00 грн</t>
+          <t>3 224.00 грн</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>155.7 грн/л</t>
+          <t>161.2 грн/л</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3 148.00 грн</t>
+          <t>3 260.00 грн</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>629.6 грн/л</t>
+          <t>652.0 грн/л</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>690.00 грн</t>
+          <t>714.00 грн</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>138.0 грн/л</t>
+          <t>142.8 грн/л</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3 424.00 грн</t>
+          <t>3 550.00 грн</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>171.2 грн/л</t>
+          <t>177.5 грн/л</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>287.00 грн</t>
+          <t>298.00 грн</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>574.0 грн/кг</t>
+          <t>596.0 грн/кг</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>187.00 грн</t>
+          <t>194.00 грн</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>748.0 грн/кг</t>
+          <t>776.0 грн/кг</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4 429.00 грн</t>
+          <t>4 586.00 грн</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>221.45 грн/л</t>
+          <t>229.3 грн/л</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3 128.00 грн</t>
+          <t>3 239.00 грн</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>625.6 грн/л</t>
+          <t>647.8 грн/л</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 515.00 грн</t>
+          <t>2 604.00 грн</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>503.0 грн/л</t>
+          <t>520.8 грн/л</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2 515.00 грн</t>
+          <t>2 604.00 грн</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>503.0 грн/л</t>
+          <t>520.8 грн/л</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>180.00 грн</t>
+          <t>186.00 грн</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>720.0 грн/кг</t>
+          <t>744.0 грн/кг</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5 171.00 грн</t>
+          <t>5 361.00 грн</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>258.55 грн/л</t>
+          <t>268.05 грн/л</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>671.00 грн</t>
+          <t>695.00 грн</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>671.0 грн/л</t>
+          <t>695.0 грн/л</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3 082.00 грн</t>
+          <t>3 192.00 грн</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>616.4 грн/л</t>
+          <t>638.4 грн/л</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3 155.00 грн</t>
+          <t>3 269.00 грн</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>631.0 грн/л</t>
+          <t>653.8 грн/л</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3 241.00 грн</t>
+          <t>3 356.00 грн</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>324.1 грн/л</t>
+          <t>335.6 грн/л</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6 627.00 грн</t>
+          <t>6 892.00 грн</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1325.4 грн/л</t>
+          <t>1378.4 грн/л</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 072.00 грн</t>
+          <t>3 181.00 грн</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>614.4 грн/л</t>
+          <t>636.2 грн/л</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2 219.00 грн</t>
+          <t>2 298.00 грн</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2219.0 грн/кг</t>
+          <t>2298.0 грн/кг</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1 854.00 грн</t>
+          <t>1 919.00 грн</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>370.8 грн/л</t>
+          <t>383.8 грн/л</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2 793.00 грн</t>
+          <t>2 892.00 грн</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>279.3 грн/л</t>
+          <t>289.2 грн/л</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1 399.00 грн</t>
+          <t>1 466.00 грн</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1399.0 грн/кг</t>
+          <t>1466.0 грн/кг</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4 836.00 грн</t>
+          <t>5 014.00 грн</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>967.2 грн/л</t>
+          <t>1002.8 грн/л</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7 369.00 грн</t>
+          <t>7 631.00 грн</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>368.45 грн/л</t>
+          <t>381.55 грн/л</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3 911.00 грн</t>
+          <t>4 050.00 грн</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>391.1 грн/л</t>
+          <t>405.0 грн/л</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1 482.00 грн</t>
+          <t>1 534.00 грн</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>296.4 грн/л</t>
+          <t>306.8 грн/л</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1 482.00 грн</t>
+          <t>1 534.00 грн</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>296.4 грн/л</t>
+          <t>306.8 грн/л</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1630,24 +1630,24 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Айлар</t>
+          <t>АЙДАХО</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16 325.00 грн</t>
+          <t>5 640.00 грн</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>816.25 грн/л</t>
+          <t>282.0 грн/л</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>аклоніфен 600г</t>
+          <t>тербутилазин 500г</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1667,39 +1667,39 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ailar-ks</t>
+          <t>https://lnzweb.com/product-aidaho</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>АКСАКАЛ</t>
+          <t>Айлар</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1 862.00 грн</t>
+          <t>16 924.00 грн</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3724.0 грн/кг</t>
+          <t>846.2 грн/л</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>флорасулам 250г</t>
+          <t>аклоніфен 600г</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1709,39 +1709,39 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-aksakal____</t>
+          <t>https://lnzweb.com/product-ailar-ks</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Альтрон, КС</t>
+          <t>АКСАКАЛ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2 141.00 грн</t>
+          <t>1 928.00 грн</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>428.2 грн/л</t>
+          <t>3856.0 грн/кг</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>альфа-циперметрин 200г</t>
+          <t>флорасулам 250г</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1751,29 +1751,29 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-altron-ks</t>
+          <t>https://lnzweb.com/product-aksakal____</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Альфа Супер</t>
+          <t>Альтрон, КС</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1 469.00 грн</t>
+          <t>2 217.00 грн</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>293.8 грн/л</t>
+          <t>443.4 грн/л</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>альфа-циперметрин 100г</t>
+          <t>альфа-циперметрин 200г</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1793,29 +1793,29 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-alfa-syper</t>
+          <t>https://lnzweb.com/product-altron-ks</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Арес, ТН</t>
+          <t>Альфа Супер</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4 749.00 грн</t>
+          <t>1 523.00 грн</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>949.8 грн/л</t>
+          <t>304.6 грн/л</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>металаксил-М 350г</t>
+          <t>альфа-циперметрин 100г</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1835,39 +1835,39 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ares-tn</t>
+          <t>https://lnzweb.com/product-alfa-syper</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Атік, ВП</t>
+          <t>Арес, ТН</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>252.00 грн</t>
+          <t>4 917.00 грн</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>504.0 грн/кг</t>
+          <t>983.4 грн/л</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ацетаміприд 200г</t>
+          <t>металаксил-М 350г</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1877,39 +1877,39 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-at-k-vp______</t>
+          <t>https://lnzweb.com/product-ares-tn</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Бантен</t>
+          <t>Атік, ВП</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8 186.00 грн</t>
+          <t>261.00 грн</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>409.3 грн/л</t>
+          <t>522.0 грн/кг</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>бентазон 480г</t>
+          <t>ацетаміприд 200г</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1919,29 +1919,29 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-banten-rk</t>
+          <t>https://lnzweb.com/product-at-k-vp______</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Бетагард</t>
+          <t>Бантен</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9 831.00 грн</t>
+          <t>8 487.00 грн</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>491.55 грн/л</t>
+          <t>424.35 грн/л</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>фенмедифам 91г</t>
+          <t>бентазон 480г</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1961,39 +1961,39 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-betagard</t>
+          <t>https://lnzweb.com/product-banten-rk</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Бомбардир Аква</t>
+          <t>Бетагард</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1 675.00 грн</t>
+          <t>10 181.00 грн</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>335.0 грн/л</t>
+          <t>509.05 грн/л</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>імідаклоприд 200г</t>
+          <t>фенмедифам 91г</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2003,29 +2003,29 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-bombardir-akva_</t>
+          <t>https://lnzweb.com/product-betagard</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Бомбардир Дуо</t>
+          <t>Бомбардир Аква</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2 793.00 грн</t>
+          <t>1 735.00 грн</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>558.6 грн/л</t>
+          <t>347.0 грн/л</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>імідаклоприд 300г</t>
+          <t>імідаклоприд 200г</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2045,29 +2045,29 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-bombardir-dyo</t>
+          <t>https://lnzweb.com/product-bombardir-akva_</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Брокс, РК</t>
+          <t>Бомбардир Дуо</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2 138.00 грн</t>
+          <t>2 892.00 грн</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>427.6 грн/л</t>
+          <t>578.4 грн/л</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>імазамокс 40г</t>
+          <t>імідаклоприд 300г</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2087,39 +2087,39 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-broks-rk_</t>
+          <t>https://lnzweb.com/product-bombardir-dyo</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Велас</t>
+          <t>Брокс, РК</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16 198.00 грн</t>
+          <t>2 217.00 грн</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>809.9 грн/л</t>
+          <t>443.4 грн/л</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>продукт ферментації гриба Steptomyces kasugaensis 60г</t>
+          <t>імазамокс 40г</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2129,39 +2129,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-velas</t>
+          <t>https://lnzweb.com/product-broks-rk_</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Вертекс</t>
+          <t>Велас</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1 761.00 грн</t>
+          <t>16 847.00 грн</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>352.2 грн/л</t>
+          <t>842.35 грн/л</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>поліетиленгліколь-400 230г</t>
+          <t>продукт ферментації гриба Steptomyces kasugaensis 60г</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2171,39 +2171,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-verteks_</t>
+          <t>https://lnzweb.com/product-velas</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Даблтрай</t>
+          <t>Вертекс</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6 917.00 грн</t>
+          <t>1 823.00 грн</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>345.85 грн/л</t>
+          <t>364.6 грн/л</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>метолахлор 960г</t>
+          <t>поліетиленгліколь-400 230г</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2213,29 +2213,29 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-dabl-trai</t>
+          <t>https://lnzweb.com/product-verteks_</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Дикамба Форте</t>
+          <t>Даблтрай</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5 473.00 грн</t>
+          <t>7 163.00 грн</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>273.65 грн/л</t>
+          <t>358.15 грн/л</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>дикамба у формі диметиламінної солі 120г</t>
+          <t>метолахлор 960г</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2255,29 +2255,29 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-dikamba-forte</t>
+          <t>https://lnzweb.com/product-dabl-trai</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Диквалан Макс</t>
+          <t>Дикамба Форте</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5 142.00 грн</t>
+          <t>5 667.00 грн</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>257.1 грн/л</t>
+          <t>283.35 грн/л</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>дикват дибромід 374г</t>
+          <t>дикамба у формі диметиламінної солі 120г</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2297,39 +2297,39 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-dikvalan-maks</t>
+          <t>https://lnzweb.com/product-dikamba-forte</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ефімер</t>
+          <t>Диквалан Макс</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1 453.00 грн</t>
+          <t>5 325.00 грн</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>290.6 грн/л</t>
+          <t>266.25 грн/л</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
+          <t>дикват дибромід 374г</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2339,39 +2339,39 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ef-mer_</t>
+          <t>https://lnzweb.com/product-dikvalan-maks</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Імпреза</t>
+          <t>Ефімер</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10 428.00 грн</t>
+          <t>1 505.00 грн</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>521.4 грн/л</t>
+          <t>301.0 грн/л</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>імазамокс 33г</t>
+          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2381,39 +2381,39 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mpreza</t>
+          <t>https://lnzweb.com/product-ef-mer_</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Кайрос</t>
+          <t>Імпреза</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>31 651.00 грн</t>
+          <t>10 811.00 грн</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6330.2 грн/л</t>
+          <t>540.55 грн/л</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>флубендіамід 480г</t>
+          <t>імазамокс 33г</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2423,29 +2423,29 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kairos</t>
+          <t>https://lnzweb.com/product-mpreza</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Камзол Турбо</t>
+          <t>Кайрос</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5 214.00 грн</t>
+          <t>32 775.00 грн</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1042.8 грн/л</t>
+          <t>6555.0 грн/л</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ципроконазол 80г</t>
+          <t>флубендіамід 480г</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2465,29 +2465,29 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kamzol-tyrbo</t>
+          <t>https://lnzweb.com/product-kairos</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Камзол, РК</t>
+          <t>Камзол Турбо</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4 842.00 грн</t>
+          <t>5 399.00 грн</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>968.4 грн/л</t>
+          <t>1079.8 грн/л</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>метконазол 60г</t>
+          <t>ципроконазол 80г</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2507,39 +2507,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kamzol-rk</t>
+          <t>https://lnzweb.com/product-kamzol-tyrbo</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Кентавр</t>
+          <t>Камзол, РК</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3 352.00 грн</t>
+          <t>5 014.00 грн</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>6704.0 грн/кг</t>
+          <t>1002.8 грн/л</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>римсульфурон 500г</t>
+          <t>метконазол 60г</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kentavr____</t>
+          <t>https://lnzweb.com/product-kamzol-rk</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Клаттер, КЕ</t>
+          <t>Кентавр</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>3 471.00 грн</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>6942.0 грн/кг</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>кломазон 480г</t>
+          <t>римсульфурон 500г</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2591,29 +2591,29 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-klatter-ke</t>
+          <t>https://lnzweb.com/product-kentavr____</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Кушон, КС</t>
+          <t>Клаттер, КЕ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4 831.00 грн</t>
+          <t>2 410.00 грн</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>966.2 грн/л</t>
+          <t>482.0 грн/л</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>метамітрон 700г</t>
+          <t>кломазон 480г</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2633,29 +2633,29 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kyshon-ks__</t>
+          <t>https://lnzweb.com/product-klatter-ke</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Латіна, ТН</t>
+          <t>Кушон, КС</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6 704.00 грн</t>
+          <t>5 003.00 грн</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1340.8 грн/л</t>
+          <t>1000.6 грн/л</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>клотіанідин 600г</t>
+          <t>метамітрон 700г</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-latina-tn</t>
+          <t>https://lnzweb.com/product-kyshon-ks__</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Літерон</t>
+          <t>Латіна, ТН</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7 187.00 грн</t>
+          <t>6 942.00 грн</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>359.35 грн/л</t>
+          <t>1388.4 грн/л</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S-метолахлор 960г</t>
+          <t>клотіанідин 600г</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2717,39 +2717,39 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-l-teron</t>
+          <t>https://lnzweb.com/product-latina-tn</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Матар, КС</t>
+          <t>Літерон</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4 372.00 грн</t>
+          <t>7 442.00 грн</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>874.4 грн/л</t>
+          <t>372.1 грн/л</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>метрибузин 600г</t>
+          <t>S-метолахлор 960г</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2759,29 +2759,29 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-matar-ks</t>
+          <t>https://lnzweb.com/product-l-teron</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Метакса</t>
+          <t>Матар, КС</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>4 532.00 грн</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>906.4 грн/л</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>тіаметоксам 350г</t>
+          <t>метрибузин 600г</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2801,29 +2801,29 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-metaksa</t>
+          <t>https://lnzweb.com/product-matar-ks</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Меценат</t>
+          <t>Метакса</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>2 410.00 грн</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>482.0 грн/л</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>пропіконазол 250г</t>
+          <t>тіаметоксам 350г</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2843,39 +2843,39 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mecenat_</t>
+          <t>https://lnzweb.com/product-metaksa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Напалм</t>
+          <t>Меценат</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3 424.00 грн</t>
+          <t>2 410.00 грн</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>171.2 грн/л</t>
+          <t>482.0 грн/л</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ізопропіламінна сіль гліфосату 480г</t>
+          <t>пропіконазол 250г</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2885,29 +2885,29 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-napalm_</t>
+          <t>https://lnzweb.com/product-mecenat_</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Напалм Форте</t>
+          <t>Напалм</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4 424.00 грн</t>
+          <t>3 550.00 грн</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>221.2 грн/л</t>
+          <t>177.5 грн/л</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>калійна сіль гліфосату 550г</t>
+          <t>ізопропіламінна сіль гліфосату 480г</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2927,29 +2927,29 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-napalm-forte_</t>
+          <t>https://lnzweb.com/product-napalm_</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Нованте</t>
+          <t>Напалм Форте</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6 517.00 грн</t>
+          <t>4 586.00 грн</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>325.85 грн/л</t>
+          <t>229.3 грн/л</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S-метолахлор 312,5г</t>
+          <t>калійна сіль гліфосату 550г</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2969,29 +2969,29 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-novante</t>
+          <t>https://lnzweb.com/product-napalm-forte_</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Оіл-Дріфт</t>
+          <t>Нованте</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5 560.00 грн</t>
+          <t>6 748.00 грн</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>278.0 грн/л</t>
+          <t>337.4 грн/л</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ріпаково-метиловий ефір 810г</t>
+          <t>S-метолахлор 312,5г</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3011,39 +3011,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-o-l-dr-ft</t>
+          <t>https://lnzweb.com/product-novante</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Парацельс</t>
+          <t>Оіл-Дріфт</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>5 757.00 грн</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>287.85 грн/л</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>флутріафол 250г</t>
+          <t>ріпаково-метиловий ефір 810г</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3053,29 +3053,29 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-paracels</t>
+          <t>https://lnzweb.com/product-o-l-dr-ft</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Пегас, КЕ</t>
+          <t>Парацельс</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>2 410.00 грн</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>482.0 грн/л</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>прохлораз 450г</t>
+          <t>флутріафол 250г</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3095,39 +3095,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-pegas-ke_</t>
+          <t>https://lnzweb.com/product-paracels</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Перун</t>
+          <t>Пегас, КЕ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5 203.00 грн</t>
+          <t>2 410.00 грн</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>260.15 грн/л</t>
+          <t>482.0 грн/л</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>прометрин 500г</t>
+          <t>прохлораз 450г</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3137,39 +3137,39 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-peryn</t>
+          <t>https://lnzweb.com/product-pegas-ke_</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Піногасник Пайот</t>
+          <t>Перун</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>615.00 грн</t>
+          <t>5 388.00 грн</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>615.0 грн/л</t>
+          <t>269.4 грн/л</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>модифікований поліефір трісілоксан 10-20 % л</t>
+          <t>прометрин 500г</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3179,39 +3179,39 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-paiot</t>
+          <t>https://lnzweb.com/product-peryn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Піраміда</t>
+          <t>Піногасник Пайот</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2 716.00 грн</t>
+          <t>637.00 грн</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>543.2 грн/л</t>
+          <t>637.0 грн/л</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>1 л</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>клопіралід 300г</t>
+          <t>модифікований поліефір трісілоксан 10-20 % л</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3221,29 +3221,29 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-p-ram-da-lontrel</t>
+          <t>https://lnzweb.com/product-paiot</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Престо</t>
+          <t>Піраміда</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3 446.00 грн</t>
+          <t>2 816.00 грн</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>689.2 грн/л</t>
+          <t>563.2 грн/л</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>клотіанідин 200г</t>
+          <t>клопіралід 300г</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3263,29 +3263,29 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-presto_</t>
+          <t>https://lnzweb.com/product-p-ram-da-lontrel</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Примус, СЕ</t>
+          <t>Престо</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1 293.00 грн</t>
+          <t>3 568.00 грн</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>258.6 грн/л</t>
+          <t>713.6 грн/л</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2-етилгексиловий ефір 2,4-Д 452г</t>
+          <t>клотіанідин 200г</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3305,39 +3305,39 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-primys_</t>
+          <t>https://lnzweb.com/product-presto_</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Просенс</t>
+          <t>Примус, СЕ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1 416.00 грн</t>
+          <t>1 341.00 грн</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2832.0 грн/кг</t>
+          <t>268.2 грн/л</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>емамектин бензоат 100г</t>
+          <t>2-етилгексиловий ефір 2,4-Д 452г</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3347,37 +3347,41 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-prostaf</t>
+          <t>https://lnzweb.com/product-primys_</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Равак</t>
+          <t>Просенс</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>358.00 грн</t>
+          <t>1 466.00 грн</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>358.0 грн/кг</t>
+          <t>2932.0 грн/кг</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1 кг</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>фольгований пакет 0.5 кг</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>емамектин бензоат 100г</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>DEFENDA</t>
@@ -3385,41 +3389,37 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ravak</t>
+          <t>https://lnzweb.com/product-prostaf</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Равак</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1 676.00 грн</t>
+          <t>371.00 грн</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3352.0 грн/кг</t>
+          <t>371.0 грн/кг</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>римсульфурон 250г</t>
-        </is>
-      </c>
+          <t>1 кг</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>DEFENDA</t>
@@ -3427,39 +3427,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-rim___</t>
+          <t>https://lnzweb.com/product-ravak</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Сальто, КС</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1 843.00 грн</t>
+          <t>1 736.00 грн</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>368.6 грн/л</t>
+          <t>3472.0 грн/кг</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>тіофанат-метил 500г</t>
+          <t>римсульфурон 250г</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3469,39 +3469,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-salto-ks_</t>
+          <t>https://lnzweb.com/product-rim___</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Сахара</t>
+          <t>Сальто, КС</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5 579.00 грн</t>
+          <t>1 908.00 грн</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>278.95 грн/л</t>
+          <t>381.6 грн/л</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ацетохлор 900г</t>
+          <t>тіофанат-метил 500г</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3511,29 +3511,29 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sahara</t>
+          <t>https://lnzweb.com/product-salto-ks_</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Сахара Супер</t>
+          <t>Сахара</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7 439.00 грн</t>
+          <t>5 784.00 грн</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>371.95 грн/л</t>
+          <t>289.2 грн/л</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ацетохлор 800г</t>
+          <t>ацетохлор 900г</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3553,39 +3553,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sahara-syper</t>
+          <t>https://lnzweb.com/product-sahara</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Синерид, МД</t>
+          <t>Сахара Супер</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5 208.00 грн</t>
+          <t>7 703.00 грн</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1041.6 грн/л</t>
+          <t>385.15 грн/л</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>тіаклоприд 240г</t>
+          <t>ацетохлор 800г</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3595,29 +3595,29 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sinerid-md_</t>
+          <t>https://lnzweb.com/product-sahara-syper</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Сілтек</t>
+          <t>Синерид, МД</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2 413.00 грн</t>
+          <t>5 399.00 грн</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>482.6 грн/л</t>
+          <t>1079.8 грн/л</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>суміш клеючих та поверхнево-активних речовин 60% р-н</t>
+          <t>тіаклоприд 240г</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3637,39 +3637,39 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-s-ltek</t>
+          <t>https://lnzweb.com/product-sinerid-md_</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Сора-Нет</t>
+          <t>Сілтек</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5 962.00 грн</t>
+          <t>2 498.00 грн</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>298.1 грн/л</t>
+          <t>499.6 грн/л</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>пропізохлор 720г</t>
+          <t>суміш клеючих та поверхнево-активних речовин 60% р-н</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3679,39 +3679,39 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sora-net</t>
+          <t>https://lnzweb.com/product-s-ltek</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Спліт</t>
+          <t>Сора-Нет</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3 631.00 грн</t>
+          <t>6 010.00 грн</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>726.2 грн/л</t>
+          <t>300.5 грн/л</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>дифеконазол 250г</t>
+          <t>пропізохлор 720г</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3721,29 +3721,29 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-spl-t</t>
+          <t>https://lnzweb.com/product-sora-net</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Старк, КС</t>
+          <t>Спліт</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2 904.00 грн</t>
+          <t>3 760.00 грн</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>580.8 грн/л</t>
+          <t>752.0 грн/л</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>азоксистробін 250г</t>
+          <t>дифеконазол 250г</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3763,29 +3763,29 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-stark-ks</t>
+          <t>https://lnzweb.com/product-spl-t</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Тава, РК</t>
+          <t>Старк, КС</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1 490.00 грн</t>
+          <t>3 007.00 грн</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>298.0 грн/л</t>
+          <t>601.4 грн/л</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>етефон 480г</t>
+          <t>азоксистробін 250г</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3805,29 +3805,29 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-tava-rk_</t>
+          <t>https://lnzweb.com/product-stark-ks</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Талер Макс</t>
+          <t>Тава, РК</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2 515.00 грн</t>
+          <t>1 543.00 грн</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>503.0 грн/л</t>
+          <t>308.6 грн/л</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>тебуконазол 500г</t>
+          <t>етефон 480г</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3847,29 +3847,29 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-taler-maks</t>
+          <t>https://lnzweb.com/product-tava-rk_</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Талер, КЕ</t>
+          <t>Талер Макс</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2 102.00 грн</t>
+          <t>2 604.00 грн</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>420.4 грн/л</t>
+          <t>520.8 грн/л</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>тебуконазол 250г</t>
+          <t>тебуконазол 500г</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3889,29 +3889,29 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-taler-ke__</t>
+          <t>https://lnzweb.com/product-taler-maks</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Топал</t>
+          <t>Талер, КЕ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5 177.00 грн</t>
+          <t>2 176.00 грн</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1035.4 грн/л</t>
+          <t>435.2 грн/л</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>трінексапак-етил 250г</t>
+          <t>тебуконазол 250г</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3931,39 +3931,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-topal</t>
+          <t>https://lnzweb.com/product-taler-ke__</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ультралін</t>
+          <t>Топал</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1 282.00 грн</t>
+          <t>5 361.00 грн</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1282.0 грн/кг</t>
+          <t>1072.2 грн/л</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>цимоксаніл 300г</t>
+          <t>трінексапак-етил 250г</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3973,39 +3973,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-yltral-n</t>
+          <t>https://lnzweb.com/product-topal</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Форит</t>
+          <t>Ультралін</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2 969.00 грн</t>
+          <t>1 327.00 грн</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>593.8 грн/л</t>
+          <t>1327.0 грн/кг</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>каністра 5 л</t>
+          <t>1 кг</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>флуроксипір 333г</t>
+          <t>цимоксаніл 300г</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4015,39 +4015,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-forit</t>
+          <t>https://lnzweb.com/product-yltral-n</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Харума</t>
+          <t>Форит</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3 537.00 грн</t>
+          <t>3 075.00 грн</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>353.7 грн/л</t>
+          <t>615.0 грн/л</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>каністра 5 л</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>хізалофоп-П-етил 125г</t>
+          <t>флуроксипір 333г</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4057,39 +4057,39 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-haryma</t>
+          <t>https://lnzweb.com/product-forit</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Хлорис, ЕН</t>
+          <t>Харума</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1 482.00 грн</t>
+          <t>3 663.00 грн</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>296.4 грн/л</t>
+          <t>366.3 грн/л</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>тебуконазол 15г</t>
+          <t>хізалофоп-П-етил 125г</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4099,29 +4099,29 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-hloris-en__</t>
+          <t>https://lnzweb.com/product-haryma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Циркуль, КЕ</t>
+          <t>Хлорис, ЕН</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1 295.00 грн</t>
+          <t>1 534.00 грн</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>259.0 грн/л</t>
+          <t>306.8 грн/л</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>лямбда-цигалотрин 50г</t>
+          <t>тебуконазол 15г</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4141,39 +4141,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-cirkyl-ke</t>
+          <t>https://lnzweb.com/product-hloris-en__</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Шериф Максі</t>
+          <t>Циркуль, КЕ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1 676.00 грн</t>
+          <t>1 341.00 грн</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3352.0 грн/кг</t>
+          <t>268.2 грн/л</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>трибенурон-метил 563г</t>
+          <t>лямбда-цигалотрин 50г</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4183,39 +4183,39 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sherif-maks</t>
+          <t>https://lnzweb.com/product-cirkyl-ke</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Шериф, ВГ</t>
+          <t>Шериф Максі</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>651.00 грн</t>
+          <t>1 736.00 грн</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1302.0 грн/л</t>
+          <t>3472.0 грн/кг</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>трибенурон-метил 750г</t>
+          <t>трибенурон-метил 563г</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sherif</t>
+          <t>https://lnzweb.com/product-sherif-maks</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4242,17 +4242,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>651.00 грн</t>
+          <t>675.00 грн</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1302.0 грн/кг</t>
+          <t>1350.0 грн/л</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>0.5 л</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4267,39 +4267,39 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sherif__</t>
+          <t>https://lnzweb.com/product-sherif</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>АЙДАХО</t>
+          <t>Шериф, ВГ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5 537.00 грн</t>
+          <t>675.00 грн</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>276.85 грн/л</t>
+          <t>1350.0 грн/кг</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>тербутилазин 500г</t>
+          <t>трибенурон-метил 750г</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-aidaho</t>
+          <t>https://lnzweb.com/product-sherif__</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1 562.00 грн</t>
+          <t>1 624.00 грн</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>312.4 грн/л</t>
+          <t>324.8 грн/л</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3 032.00 грн</t>
+          <t>3 154.00 грн</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303.2 грн/л</t>
+          <t>315.4 грн/л</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>442.00 грн</t>
+          <t>463.00 грн</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4420.0 грн/кг</t>
+          <t>4630.0 грн/кг</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1 674.00 грн</t>
+          <t>1 741.00 грн</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>334.8 грн/л</t>
+          <t>348.2 грн/л</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4 682.00 грн</t>
+          <t>4 870.00 грн</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>468.2 грн/л</t>
+          <t>487.0 грн/л</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4534,16 +4534,8 @@
           <t>Брокс, РК</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>4 685.00 грн</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>468.5 грн/л</t>
-        </is>
-      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>10 л</t>
@@ -4566,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4570,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6 157.00 грн</t>
+          <t>6 404.00 грн</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>307.85 грн/л</t>
+          <t>320.2 грн/л</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4608,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4612,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>9 529.00 грн</t>
+          <t>9 910.00 грн</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>952.9 грн/л</t>
+          <t>991.0 грн/л</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4650,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4654,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>33 904.00 грн</t>
+          <t>35 262.00 грн</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1695.2 грн/л</t>
+          <t>1763.1 грн/л</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4692,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4696,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12 491.00 грн</t>
+          <t>12 991.00 грн</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>624.55 грн/л</t>
+          <t>649.55 грн/л</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4734,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4738,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5 710.00 грн</t>
+          <t>5 939.00 грн</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>571.0 грн/л</t>
+          <t>593.9 грн/л</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4776,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4780,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4 015.00 грн</t>
+          <t>4 176.00 грн</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>401.5 грн/л</t>
+          <t>417.6 грн/л</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4818,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4830,12 +4822,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>937.00 грн</t>
+          <t>975.00 грн</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>187.4 грн/л</t>
+          <t>195.0 грн/л</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4860,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4872,12 +4864,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>937.00 грн</t>
+          <t>975.00 грн</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>187.4 грн/л</t>
+          <t>195.0 грн/л</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4902,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4906,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2 762.00 грн</t>
+          <t>2 872.00 грн</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4603.33 грн/кг</t>
+          <t>4786.67 грн/кг</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4944,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4948,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1 451.00 грн</t>
+          <t>1 509.00 грн</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>290.2 грн/л</t>
+          <t>301.8 грн/л</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4986,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -4998,12 +4990,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>137.00 грн</t>
+          <t>142.00 грн</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>685.0 грн/л</t>
+          <t>710.0 грн/л</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5028,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5032,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16 060.00 грн</t>
+          <t>16 703.00 грн</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>803.0 грн/л</t>
+          <t>835.15 грн/л</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5070,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5074,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>821.00 грн</t>
+          <t>854.00 грн</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>821.0 грн/л</t>
+          <t>854.0 грн/л</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5112,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5124,12 +5116,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3 792.00 грн</t>
+          <t>3 944.00 грн</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>379.2 грн/л</t>
+          <t>394.4 грн/л</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5154,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5158,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6 669.00 грн</t>
+          <t>6 793.00 грн</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>333.45 грн/л</t>
+          <t>339.65 грн/л</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5196,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5208,12 +5200,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>4 417.00 грн</t>
+          <t>4 594.00 грн</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>441.7 грн/л</t>
+          <t>459.4 грн/л</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5238,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5242,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4 020.00 грн</t>
+          <t>4 163.00 грн</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>402.0 грн/л</t>
+          <t>416.3 грн/л</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5280,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5360,12 +5352,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>11 154.00 грн</t>
+          <t>11 600.00 грн</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>557.7 грн/л</t>
+          <t>580.0 грн/л</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5390,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5394,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>650.00 грн</t>
+          <t>676.00 грн</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>650.0 грн/кг</t>
+          <t>676.0 грн/кг</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5432,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5436,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2 209.00 грн</t>
+          <t>2 297.00 грн</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>441.8 грн/л</t>
+          <t>459.4 грн/л</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5474,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5478,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3 079.00 грн</t>
+          <t>3 202.00 грн</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>307.9 грн/л</t>
+          <t>320.2 грн/л</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5516,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48</t>
+          <t>2026-10-06 10:44</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-06 10:44</t>
+          <t>2026-10-07 10:32</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32</t>
+          <t>2026-10-08 10:53</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53</t>
+          <t>2026-10-09 10:52</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-09 10:52</t>
+          <t>2026-10-10 10:06</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-10 10:06</t>
+          <t>2026-10-11 10:17</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17</t>
+          <t>2026-10-12 11:17</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-12 11:17</t>
+          <t>2026-10-13 11:01</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01</t>
+          <t>2026-10-14 08:59</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-14 08:59</t>
+          <t>2026-10-15 08:33</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-15 08:33</t>
+          <t>2026-10-16 08:28</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-16 08:28</t>
+          <t>2026-10-17 08:00</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00</t>
+          <t>2026-10-18 08:18</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-18 08:18</t>
+          <t>2026-10-19 09:16</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-19 09:16</t>
+          <t>2026-10-20 08:50</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-20 08:50</t>
+          <t>2026-10-21 08:50</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 08:50</t>
+          <t>2026-10-22 08:53</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-22 08:53</t>
+          <t>2026-10-23 08:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-23 08:48</t>
+          <t>2026-10-24 08:22</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-24 08:22</t>
+          <t>2026-10-25 08:41</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-25 08:41</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 09:18</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18</t>
+          <t>2026-10-28 09:59</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59</t>
+          <t>2026-10-29 10:21</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21</t>
+          <t>2026-10-30 10:24</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24</t>
+          <t>2026-10-31 09:55</t>
         </is>
       </c>
     </row>
